--- a/templates/data-collection-template.xlsx
+++ b/templates/data-collection-template.xlsx
@@ -378,7 +378,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TJS data-collection template</t>
+          <t>HFR Ortho data-collection template</t>
         </is>
       </c>
     </row>
@@ -399,7 +399,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Never type patient names or MRNs here. Use the study ID; keep the MRN-to-study-ID crosswalk in a separate, secured file.</t>
+          <t>2. Never type patient names or patient numbers here. Use the study code; the project lead keeps the code key (patient number to study code) in a separate, secured file.</t>
         </is>
       </c>
     </row>

--- a/templates/data-collection-template.xlsx
+++ b/templates/data-collection-template.xlsx
@@ -399,7 +399,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Never type patient names or patient numbers here. Use the study code; the project lead keeps the code key (patient number to study code) in a separate, secured file.</t>
+          <t>2. Never type patient names or patient numbers here. Use the study code; the code key (patient number to study code) is kept in a separate, secured file by the person the ethics application names for it.</t>
         </is>
       </c>
     </row>

--- a/templates/data-collection-template.xlsx
+++ b/templates/data-collection-template.xlsx
@@ -399,7 +399,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Never type patient names or patient numbers here. Use the study code; the code key (patient number to study code) is kept in a separate, secured file by the person the ethics application names for it.</t>
+          <t>2. Never type patient names or patient numbers here. Use the study code; the code key (patient number to study code) is kept in a separate, secured file by the person the ethics application names for it, who isn't involved in the project.</t>
         </is>
       </c>
     </row>
